--- a/data/trans_bre/IP08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 0,61</t>
+          <t>-9,73; 1,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 4,79</t>
+          <t>-7,39; 4,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 4,45</t>
+          <t>-5,04; 4,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-28,77; 2,45</t>
+          <t>-29,28; 2,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,03; 7,71</t>
+          <t>-68,73; 18,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-55,97; 58,04</t>
+          <t>-52,69; 57,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-59,03; 109,24</t>
+          <t>-59,85; 137,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-79,76; 28,8</t>
+          <t>-87,51; 32,91</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,07; -0,68</t>
+          <t>-10,0; -0,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 4,45</t>
+          <t>-6,43; 4,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 4,89</t>
+          <t>-4,08; 4,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 11,04</t>
+          <t>-4,2; 10,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,64; -5,16</t>
+          <t>-61,58; -1,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 41,38</t>
+          <t>-37,33; 42,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 73,89</t>
+          <t>-36,15; 74,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,92; 124,09</t>
+          <t>-36,11; 122,31</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 0,26</t>
+          <t>-9,74; 0,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 3,92</t>
+          <t>-8,84; 3,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 5,32</t>
+          <t>-3,16; 4,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 1,8</t>
+          <t>-9,88; 2,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-73,33; 5,78</t>
+          <t>-74,69; 5,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,76; 33,02</t>
+          <t>-46,45; 33,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 162,33</t>
+          <t>-43,24; 153,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-65,69; 28,36</t>
+          <t>-65,4; 36,71</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 5,53</t>
+          <t>-5,03; 5,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 1,65</t>
+          <t>-8,6; 2,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 3,04</t>
+          <t>-4,72; 3,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 0,09</t>
+          <t>-12,58; -0,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,79; 63,23</t>
+          <t>-37,71; 62,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,9; 15,05</t>
+          <t>-53,83; 20,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,92; 75,7</t>
+          <t>-59,14; 78,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,57; 2,2</t>
+          <t>-64,08; -1,23</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; -0,73</t>
+          <t>-5,85; -0,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,8</t>
+          <t>-4,6; 1,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,95</t>
+          <t>-2,51; 1,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,0; -0,02</t>
+          <t>-8,46; -0,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,33; -6,67</t>
+          <t>-45,83; -4,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,06; 7,29</t>
+          <t>-30,91; 8,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,63; 33,25</t>
+          <t>-31,72; 34,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 2,13</t>
+          <t>-50,79; 1,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 1,34</t>
+          <t>-10,49; 1,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 4,77</t>
+          <t>-8,26; 4,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 4,81</t>
+          <t>-5,08; 4,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 2,71</t>
+          <t>-27,16; 2,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,73; 18,29</t>
+          <t>-69,36; 17,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-52,69; 57,0</t>
+          <t>-53,53; 50,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-59,85; 137,65</t>
+          <t>-59,02; 100,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-87,51; 32,91</t>
+          <t>-82,07; 29,88</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,0; -0,26</t>
+          <t>-10,06; -0,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 4,66</t>
+          <t>-5,89; 4,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 4,73</t>
+          <t>-3,68; 5,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 10,78</t>
+          <t>-4,0; 11,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,58; -1,98</t>
+          <t>-62,84; -6,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,33; 42,11</t>
+          <t>-34,22; 39,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,15; 74,75</t>
+          <t>-33,9; 82,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,11; 122,31</t>
+          <t>-35,64; 131,51</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 0,29</t>
+          <t>-10,3; 0,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 3,71</t>
+          <t>-8,2; 3,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 4,91</t>
+          <t>-3,66; 4,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 2,79</t>
+          <t>-10,98; 1,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-74,69; 5,05</t>
+          <t>-74,18; 9,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 33,24</t>
+          <t>-46,11; 30,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-43,24; 153,21</t>
+          <t>-49,92; 133,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-65,4; 36,71</t>
+          <t>-70,97; 22,54</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 5,16</t>
+          <t>-5,06; 5,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 2,23</t>
+          <t>-8,81; 2,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 3,25</t>
+          <t>-5,07; 2,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,58; -0,34</t>
+          <t>-12,47; -0,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 62,04</t>
+          <t>-37,68; 65,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,83; 20,14</t>
+          <t>-53,47; 22,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,14; 78,55</t>
+          <t>-62,32; 64,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,08; -1,23</t>
+          <t>-64,0; 1,94</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,85; -0,44</t>
+          <t>-5,86; -0,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 1,04</t>
+          <t>-4,73; 0,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,99</t>
+          <t>-2,53; 2,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,46; -0,05</t>
+          <t>-7,98; 0,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,83; -4,44</t>
+          <t>-45,94; -3,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 8,28</t>
+          <t>-32,0; 6,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 34,75</t>
+          <t>-32,16; 34,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-50,79; 1,26</t>
+          <t>-50,96; 1,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,81</t>
+          <t>-6,05</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-39,93%</t>
+          <t>-36,94%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 1,02</t>
+          <t>-10,77; 0,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 4,29</t>
+          <t>-8,14; 4,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 4,62</t>
+          <t>-5,22; 4,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 2,5</t>
+          <t>-25,04; 2,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-69,36; 17,3</t>
+          <t>-73,03; 7,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-53,53; 50,29</t>
+          <t>-55,97; 58,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-59,02; 100,84</t>
+          <t>-59,03; 109,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-82,07; 29,88</t>
+          <t>-77,5; 28,79</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>-11,72%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,06; -0,81</t>
+          <t>-10,07; -0,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 4,38</t>
+          <t>-5,69; 4,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 5,33</t>
+          <t>-3,95; 4,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 11,12</t>
+          <t>-6,07; 3,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,84; -6,34</t>
+          <t>-62,64; -5,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 39,81</t>
+          <t>-34,07; 41,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,9; 82,61</t>
+          <t>-32,67; 73,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,64; 131,51</t>
+          <t>-50,42; 43,52</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,64</t>
+          <t>-2,32</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-32,19%</t>
+          <t>-19,71%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 0,13</t>
+          <t>-9,68; 0,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 3,61</t>
+          <t>-8,67; 3,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 4,51</t>
+          <t>-2,98; 5,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 1,88</t>
+          <t>-8,7; 3,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-74,18; 9,71</t>
+          <t>-73,33; 5,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,11; 30,24</t>
+          <t>-46,76; 33,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-49,92; 133,98</t>
+          <t>-41,9; 162,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-70,97; 22,54</t>
+          <t>-55,32; 53,51</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-6,23</t>
+          <t>-5,43</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-40,04%</t>
+          <t>-36,68%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 5,33</t>
+          <t>-4,54; 5,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 2,2</t>
+          <t>-8,61; 1,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 2,52</t>
+          <t>-4,88; 3,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,47; -0,05</t>
+          <t>-10,82; 0,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 65,39</t>
+          <t>-35,79; 63,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,47; 22,07</t>
+          <t>-52,9; 15,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,32; 64,74</t>
+          <t>-59,92; 75,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,0; 1,94</t>
+          <t>-61,82; 9,83</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,47</t>
+          <t>-3,32</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-26,65%</t>
+          <t>-26,1%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,86; -0,43</t>
+          <t>-5,95; -0,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,76</t>
+          <t>-5,1; 0,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,06</t>
+          <t>-2,54; 1,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 0,14</t>
+          <t>-7,49; -0,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,94; -3,92</t>
+          <t>-45,33; -6,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 6,13</t>
+          <t>-32,06; 7,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 34,95</t>
+          <t>-31,63; 33,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-50,96; 1,33</t>
+          <t>-47,18; -3,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-4,42</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,56</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-6,05</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-38,56%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-13,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-8,17%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-36,94%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-4.417201396795479</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.56122195541158</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.543687839520815</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-6.053542631397013</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.385559585279085</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1339628130461178</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.08171819384685763</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.3694011579272887</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-10,77; 0,61</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-8,14; 4,79</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,22; 4,45</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-25,04; 2,5</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-73,03; 7,71</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-55,97; 58,04</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-59,03; 109,24</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-77,5; 28,79</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-10.77181077794446</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-8.143776510007859</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.217831116104023</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-25.03995422136917</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.7302627109478504</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.5596727441866213</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.590276387844453</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.7750334298386492</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.6102209911733407</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.785112705854935</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.45461532316194</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2.502336107817923</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.07705280016475421</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.580384470389345</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.092438112196405</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.2878562266904311</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-5,33</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,16</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-39,84%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-4,01%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-11,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-10,07; -0,68</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,69; 4,45</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,95; 4,89</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-6,07; 3,3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-62,64; -5,16</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-34,07; 41,38</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-32,67; 73,89</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-50,42; 43,52</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-5.325845249445589</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.5635809410814624</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.5447460043775874</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.162336633482883</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.3983977520539327</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.04014621471765334</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.06098563373140271</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1171957395323672</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-4,56</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,39</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,67</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,32</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-44,39%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-15,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-19,71%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-10.06861252950065</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.68607769328875</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.951096497812037</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-6.074905657238363</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6263641621555308</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3407076218755656</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3267318655272575</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5042032437316458</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-9,68; 0,26</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-8,67; 3,92</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,98; 5,32</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-8,7; 3,72</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-73,33; 5,78</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-46,76; 33,02</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-41,9; 162,33</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-55,32; 53,51</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-0.6825569738475116</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.448163769390759</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.889721544062355</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.303271564313826</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.05155409279725124</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.413752196919836</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.7389443015852767</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.4352349136791944</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-3,2</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-5,43</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-24,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-18,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-36,68%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-4.557799066145521</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.394286175421742</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.6692309570575962</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-2.324515316716137</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.4438956922131873</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1576974831889589</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.1223146650585096</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.1970579190383061</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,54; 5,53</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-8,61; 1,65</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,88; 3,04</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-10,82; 0,92</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-35,79; 63,23</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-52,9; 15,05</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-59,92; 75,7</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-61,82; 9,83</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.677323114495003</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.673538811138107</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.981464608522023</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-8.695767222032892</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.7332937534695171</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4676405043480887</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4190142304643573</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5531961650887807</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2563141090110322</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.922206087956133</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.317631605507298</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.719475197216437</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.05778416507090026</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.3302041970903202</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.623283662090738</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.535067251061712</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.2216116092592813</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-3.198944929037447</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.126696505285392</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-5.430475014395634</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.0206631497388806</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2408709455499342</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1835541898755296</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.3668444863904052</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.538276864062498</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-8.613830518488495</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.880691260156222</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-10.82306208499231</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3578875469685188</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5290367981822069</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5991847018736656</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.618190377597681</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.532032854242567</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.651128757411914</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.039452862244772</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.9206963113735389</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.632266795121149</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1505334363701844</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.7570010574053981</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.09831173568081336</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-3,3</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,93</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-28,57%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-14,21%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-2,17%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-26,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,95; -0,73</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-5,1; 0,8</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,54; 1,95</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-7,49; -0,45</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-45,33; -6,67</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-32,06; 7,29</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-31,63; 33,25</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-47,18; -3,11</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-3.303284523888862</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.93139494561889</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.1506005161089757</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-3.319506118725754</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2857033034022324</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1420942007687196</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.02171392135158616</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.2609506388123771</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.954563579236132</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-5.095376117697031</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.540201451966159</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-7.492676257237084</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4532507148042993</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3205734876191109</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.3163209210827836</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.4718355910527177</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>-0.7259770895151286</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.8021662693662933</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.946767346675045</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-0.4480021886639322</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-0.06674571181138882</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.07287206935443569</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.3325198694159462</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>-0.03114226194607941</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
